--- a/Stats Sheet/Round Gaps/UHC Prime.xlsx
+++ b/Stats Sheet/Round Gaps/UHC Prime.xlsx
@@ -100,18 +100,15 @@
     <x:t>358</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>LightningS7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lottebunny</x:t>
   </x:si>
   <x:si>
     <x:t>312</x:t>
   </x:si>
   <x:si>
-    <x:t>LightningS7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lottebunny</x:t>
-  </x:si>
-  <x:si>
     <x:t>MeadowMoos</x:t>
   </x:si>
   <x:si>
@@ -119,6 +116,9 @@
   </x:si>
   <x:si>
     <x:t>natsuvi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>nsket</x:t>
@@ -1040,19 +1040,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1060,15 +1051,30 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -1083,24 +1089,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K18" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -1132,9 +1123,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -1149,7 +1158,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>8</x:v>
@@ -1160,17 +1169,8 @@
       <x:c r="G21" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1248,7 +1248,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1540,7 +1540,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
         <x:v>8</x:v>
@@ -1724,7 +1724,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
         <x:v>8</x:v>
